--- a/data/escolaridades.xlsx
+++ b/data/escolaridades.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colaboragov-my.sharepoint.com/personal/wesley_jesus_gestao_gov_br/Documents/Documentos/Indigenas/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_EC60FDCE8F79A8D366075C52F32BF271D9E4A886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916A1FCB-9B18-4DED-9545-8CA4B4810418}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_EC60FDCE8F79A8D366075C52F32BF271D9E4A886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF180F9-90AE-481E-A573-DA58CBDE4FBE}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
+    <sheet name="ordens" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/escolaridades.xlsx
+++ b/data/escolaridades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colaboragov-my.sharepoint.com/personal/wesley_jesus_gestao_gov_br/Documents/Documentos/Indigenas/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_EC60FDCE8F79A8D366075C52F32BF271D9E4A886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF180F9-90AE-481E-A573-DA58CBDE4FBE}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_EC60FDCE8F79A8D366075C52F32BF271D9E4A886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42BD34C9-94B5-4499-B48D-61E683A86063}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="48">
   <si>
     <t>escolaridade</t>
   </si>
@@ -42,9 +42,6 @@
     <t>nome_escolaridade</t>
   </si>
   <si>
-    <t>total</t>
-  </si>
-  <si>
     <t>ENSINO FUNDAMENTAL INCOMPLE</t>
   </si>
   <si>
@@ -127,6 +124,60 @@
   </si>
   <si>
     <t>ordem</t>
+  </si>
+  <si>
+    <t>ANALFABETO</t>
+  </si>
+  <si>
+    <t>PRIMEIRO GRAU INCOMP.-ATE A</t>
+  </si>
+  <si>
+    <t>4A. SERIE DO PRIMEIRO GRAU</t>
+  </si>
+  <si>
+    <t>APERFEICOAMENTO NIVEL MEDIO</t>
+  </si>
+  <si>
+    <t>ESPECIALIZACAO NIVEL MEDIO(</t>
+  </si>
+  <si>
+    <t>APERFEICOAMENTO NIVEL SUPER</t>
+  </si>
+  <si>
+    <t>POS-DOUTORADO(T)</t>
+  </si>
+  <si>
+    <t>ESPECIALIZACAO (RMI)(T)</t>
+  </si>
+  <si>
+    <t>AUXILIAR DE ENFERMAGEM(T)</t>
+  </si>
+  <si>
+    <t>LICENCIATURA PLENA(T)</t>
+  </si>
+  <si>
+    <t>APERFEICOAMENTO PROFISSIONA</t>
+  </si>
+  <si>
+    <t>CURSO CAPACIT/QUALIFIC PROF</t>
+  </si>
+  <si>
+    <t>ESPECIALIZACAO LATO SENSU(T</t>
+  </si>
+  <si>
+    <t>POS-GRADUACAO LATO SENSU(T)</t>
+  </si>
+  <si>
+    <t>TECNOLOGO(T)</t>
+  </si>
+  <si>
+    <t>S/Info</t>
+  </si>
+  <si>
+    <t>Não Alfabetizado</t>
+  </si>
+  <si>
+    <t>Pós-Doutorado</t>
   </si>
 </sst>
 </file>
@@ -479,14 +530,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,421 +546,584 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>151</v>
-      </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="E3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>80</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>546</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>641</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>346</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>48</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>50</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>53</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>58</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25">
-        <v>31</v>
-      </c>
-      <c r="D25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC0C276-2F13-4ABB-A00E-EC433DC8AC3E}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -926,7 +1141,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -934,7 +1149,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -942,7 +1157,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -950,7 +1165,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -958,7 +1173,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -966,7 +1181,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -974,10 +1189,34 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
